--- a/ejercicios/ej03_redes.xlsx
+++ b/ejercicios/ej03_redes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tardes\Desktop\compartida\modulo-i\ejercicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D4A83AD-4399-4EF5-A12F-B763E5A5C661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9A01C0-0B40-4F8E-B226-95D6CD983CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{35FD51AA-1F96-48D2-AE7A-F53BE8765BA1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>12.34.0.0/16</t>
   </si>
@@ -81,13 +81,85 @@
   </si>
   <si>
     <t>BC</t>
+  </si>
+  <si>
+    <t>Departamento</t>
+  </si>
+  <si>
+    <t>Dir.SubRed/x</t>
+  </si>
+  <si>
+    <t>Mascara</t>
+  </si>
+  <si>
+    <t>Difusion</t>
+  </si>
+  <si>
+    <t>Rango</t>
+  </si>
+  <si>
+    <t>Dirección</t>
+  </si>
+  <si>
+    <t>Producción</t>
+  </si>
+  <si>
+    <t>Administración</t>
+  </si>
+  <si>
+    <t>Invitados 1</t>
+  </si>
+  <si>
+    <t>Invitados 2</t>
+  </si>
+  <si>
+    <t>255.255.240.0</t>
+  </si>
+  <si>
+    <t>12.34.15.255</t>
+  </si>
+  <si>
+    <t>12.34.0.0/20</t>
+  </si>
+  <si>
+    <t>12.34.16.0/21</t>
+  </si>
+  <si>
+    <t>255.255.248.0</t>
+  </si>
+  <si>
+    <t>12.34.23.255</t>
+  </si>
+  <si>
+    <t>12.34.24.0/22</t>
+  </si>
+  <si>
+    <t>255.255.252.0</t>
+  </si>
+  <si>
+    <t>12.34.27.255</t>
+  </si>
+  <si>
+    <t>12.34.28.0/26</t>
+  </si>
+  <si>
+    <t>255.255.255.192</t>
+  </si>
+  <si>
+    <t>12.34.28.63</t>
+  </si>
+  <si>
+    <t>12.34.28.64/26</t>
+  </si>
+  <si>
+    <t>12.34.28.127</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,16 +167,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -112,13 +204,157 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,12 +689,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE0970E7-F9C8-4756-A6ED-2F2BE2CF52F0}">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="5" width="5.42578125" customWidth="1"/>
     <col min="6" max="6" width="3.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -917,7 +1156,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="33" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H33">
         <v>12</v>
       </c>
@@ -931,7 +1170,101 @@
         <v>255</v>
       </c>
     </row>
+    <row r="34" spans="8:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L37" s="2"/>
+    </row>
+    <row r="38" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H38" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L39" s="2"/>
+    </row>
+    <row r="40" spans="8:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K40" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L40" s="3"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>